--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,18 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -209,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -225,40 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -285,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -294,22 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -332,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -342,17 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -366,18 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -811,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -908,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -919,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -937,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -978,7 +883,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1037,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1045,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1077,31 +982,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1134,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1148,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1160,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1213,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1222,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1263,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1313,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1322,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1363,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1372,37 +1277,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="P5" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1413,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1422,37 +1327,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1463,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1472,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1501,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1513,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1522,137 +1427,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="6" t="s">
-        <x:v>74</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -137,15 +137,10 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -972,13 +967,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1080,13 +1075,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1098,10 +1093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1160,49 +1155,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1213,7 +1208,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1222,31 +1217,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1263,7 +1258,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1272,31 +1267,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1313,7 +1308,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1322,31 +1317,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1363,7 +1358,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1372,34 +1367,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1413,7 +1408,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1422,31 +1417,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1463,7 +1458,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1472,22 +1467,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1513,7 +1508,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1522,37 +1517,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1560,7 +1555,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1587,22 +1582,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1610,7 +1605,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1637,22 +1632,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="6" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -137,10 +137,11 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
+    <x:t xml:space="preserve">Unhandled exception. System.Net.Sockets.SocketException (98): Address already in use
+   at System.Net.Sockets.Socket.DoBind(EndPoint endPointSnapshot, SocketAddress socketAddress)
+   at System.Net.Sockets.Socket.Bind(EndPoint localEP)
+   at System.Net.Sockets.TcpListener.Start(Int32 backlog)
+   at Program.&lt;Main&gt;$(String[] args)
 </x:t>
   </x:si>
   <x:si>
@@ -229,28 +230,25 @@
 </x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK, RST</x:t>
   </x:si>
   <x:si>
     <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK, FIN</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>RST</x:t>
@@ -280,7 +278,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -295,11 +293,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -327,7 +320,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -343,11 +336,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -369,10 +359,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -967,13 +953,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="91.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1075,13 +1061,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1093,10 +1079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1129,7 +1115,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1155,49 +1141,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="D1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="O1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1208,40 +1194,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="J2" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="M2" s="0" t="s">
+      <x:c r="N2" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1258,7 +1244,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1267,31 +1253,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1308,7 +1294,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1317,31 +1303,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="K4" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="M4" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1358,7 +1344,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1367,34 +1353,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
+      <x:c r="L5" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="O5" s="2" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1408,7 +1394,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1417,37 +1403,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1458,7 +1444,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1467,22 +1453,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1508,7 +1494,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1517,37 +1503,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>73</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1555,7 +1541,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1582,22 +1568,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="L9" s="0" t="s">
+      <x:c r="M9" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="M9" s="0" t="s">
+      <x:c r="N9" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="6" t="s">
-        <x:v>75</x:v>
+      <x:c r="P9" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1605,49 +1591,149 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
+      <x:c r="L12" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="6" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,14 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unhandled exception. System.Net.Sockets.SocketException (98): Address already in use
-   at System.Net.Sockets.Socket.DoBind(EndPoint endPointSnapshot, SocketAddress socketAddress)
-   at System.Net.Sockets.Socket.Bind(EndPoint localEP)
-   at System.Net.Sockets.TcpListener.Start(Int32 backlog)
-   at Program.&lt;Main&gt;$(String[] args)
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -205,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -221,37 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -278,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -287,17 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -320,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -330,14 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -351,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -792,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -889,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -900,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -918,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -959,7 +883,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="91.282054" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1018,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1026,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1058,31 +982,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1115,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1129,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1141,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1194,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1203,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1244,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1294,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1303,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1344,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1353,34 +1277,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1394,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1403,22 +1327,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1432,8 +1356,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1444,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1453,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1482,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1494,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1503,22 +1427,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1532,208 +1456,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="s">
-        <x:v>69</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -121,6 +137,13 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,25 +204,50 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 + 2
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -226,7 +274,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -235,7 +283,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -258,7 +316,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -268,8 +326,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -283,6 +347,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -716,13 +788,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -813,7 +885,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -824,13 +896,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -842,10 +914,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -877,13 +949,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -942,7 +1014,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -950,16 +1022,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -971,7 +1043,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -982,7 +1054,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1003,10 +1075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1039,11 +1111,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P8"/>
+  <x:dimension ref="A1:P12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1053,7 +1125,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1065,49 +1137,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1118,7 +1190,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1127,31 +1199,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1168,7 +1240,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1177,31 +1249,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1218,7 +1290,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,31 +1299,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1268,7 +1340,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1277,34 +1349,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O5" s="2" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1318,7 +1390,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1327,22 +1399,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1356,8 +1428,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1368,7 +1440,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,22 +1449,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1406,8 +1478,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P7" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1418,7 +1490,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,37 +1499,237 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="L9" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="M9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -220,34 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -274,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -283,17 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -316,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -326,14 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -347,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -788,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -885,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -896,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -914,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -949,13 +877,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1014,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1022,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1054,7 +982,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1075,10 +1003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1111,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1125,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1137,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1190,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1199,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1240,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1290,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1299,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1340,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1349,34 +1277,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1390,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1399,22 +1327,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1428,8 +1356,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1440,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1449,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1478,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1490,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1499,22 +1427,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1528,208 +1456,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="s">
-        <x:v>69</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/GradeDetail.xlsx
@@ -108,22 +108,6 @@
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -131,13 +115,15 @@
 Client disconnected</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Client connected
+Client disconnected
+</x:t>
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Waiting for a connection from client
@@ -226,7 +212,7 @@
 </x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
+    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>(Not validated by this test case)</x:t>
@@ -235,19 +221,13 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
+    <x:t>3</x:t>
   </x:si>
   <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -288,7 +268,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -782,8 +762,8 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
@@ -896,13 +876,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -914,10 +894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -943,8 +923,8 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
@@ -1014,7 +994,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1022,16 +1002,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1043,10 +1023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S2" s="2" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -1054,7 +1034,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1075,10 +1055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1111,7 +1091,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1124,8 +1104,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1137,49 +1117,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1190,7 +1170,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1199,31 +1179,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1240,40 +1220,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1290,7 +1270,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1299,31 +1279,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1340,7 +1320,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1349,34 +1329,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1390,7 +1370,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1399,37 +1379,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="4" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1440,7 +1420,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1449,37 +1429,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O7" s="2" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1490,7 +1470,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1499,37 +1479,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1537,7 +1517,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1564,22 +1544,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1587,7 +1567,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1614,22 +1594,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1637,7 +1617,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1664,22 +1644,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1687,7 +1667,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>17</x:v>
@@ -1714,22 +1694,372 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:16">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N12" s="0" t="s">
+      <x:c r="L14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:16">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="s">
-        <x:v>69</x:v>
+      <x:c r="M15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:16">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:16">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:16">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:16">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
